--- a/figures/Figure2/data/experiments/experimental_andesitesH2O.xlsx
+++ b/figures/Figure2/data/experiments/experimental_andesitesH2O.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiacovino/PythonGit/EoV_CH2-2/SaturdayNightFun/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kiacovino/PythonGit/EoV_CH2-2/figures/Figure2/data/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB4156A-AAFB-5E42-89FD-46234FC0C6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D59F573-20F3-0C44-89A1-92754492C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12620" yWindow="29360" windowWidth="29920" windowHeight="18780" xr2:uid="{BB60B309-F90E-6740-9304-3B7CB1B6F6B9}"/>
+    <workbookView xWindow="12620" yWindow="34480" windowWidth="29920" windowHeight="18780" xr2:uid="{BB60B309-F90E-6740-9304-3B7CB1B6F6B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>Hamilton et al 1964</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Hamilton et al., 1967</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>A14**</t>
   </si>
   <si>
@@ -65,15 +62,9 @@
     <t>Citation</t>
   </si>
   <si>
-    <t>Rock Type</t>
-  </si>
-  <si>
     <t>Simplified Rock Type</t>
   </si>
   <si>
-    <t>vols</t>
-  </si>
-  <si>
     <t>T_C</t>
   </si>
   <si>
@@ -138,6 +129,15 @@
   </si>
   <si>
     <t>PE-M12-20†</t>
+  </si>
+  <si>
+    <t>ST18 #3-1</t>
+  </si>
+  <si>
+    <t>Iacono-Marziano et al. 2008</t>
+  </si>
+  <si>
+    <t>Reference Number</t>
   </si>
 </sst>
 </file>
@@ -207,7 +207,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -217,6 +216,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,764 +554,728 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E12FD96-9E55-654E-9E73-5475954E80E6}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="str">
-        <f>IF(S2=0,"H2O",IF(R2&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
+      <c r="E2" s="2">
+        <v>1100</v>
       </c>
       <c r="F2" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G2" s="2">
         <v>3000</v>
       </c>
-      <c r="H2" s="4">
+      <c r="G2" s="3">
         <v>58.41</v>
       </c>
-      <c r="I2" s="4">
+      <c r="H2" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="J2" s="4">
+      <c r="I2" s="3">
         <v>18.25</v>
       </c>
-      <c r="K2" s="4">
+      <c r="J2" s="3">
         <v>6.46</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3">
         <v>3.39</v>
       </c>
-      <c r="N2" s="4">
+      <c r="M2" s="3">
         <v>6.7</v>
       </c>
-      <c r="O2" s="4">
+      <c r="N2" s="3">
         <v>4.3499999999999996</v>
       </c>
-      <c r="P2" s="4">
+      <c r="O2" s="3">
         <v>0.82</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="P2" s="3">
         <v>0.26</v>
       </c>
-      <c r="R2" s="4">
+      <c r="Q2" s="3">
         <v>7.4</v>
       </c>
-      <c r="S2" s="5"/>
-    </row>
-    <row r="3" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R2" s="4"/>
+    </row>
+    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="str">
-        <f>IF(S3=0,"H2O",IF(R3&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
+      <c r="E3" s="2">
+        <v>1100</v>
       </c>
       <c r="F3" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G3" s="2">
         <v>3000</v>
       </c>
-      <c r="H3" s="4">
+      <c r="G3" s="3">
         <v>58.41</v>
       </c>
-      <c r="I3" s="4">
+      <c r="H3" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="J3" s="4">
+      <c r="I3" s="3">
         <v>18.25</v>
       </c>
-      <c r="K3" s="4">
+      <c r="J3" s="3">
         <v>6.3097000000000003</v>
       </c>
-      <c r="L3" s="4">
+      <c r="K3" s="3">
         <v>0.1</v>
       </c>
-      <c r="M3" s="4">
+      <c r="L3" s="3">
         <v>3.39</v>
       </c>
-      <c r="N3" s="4">
+      <c r="M3" s="3">
         <v>6.7</v>
       </c>
-      <c r="O3" s="4">
+      <c r="N3" s="3">
         <v>4.3499999999999996</v>
       </c>
-      <c r="P3" s="4">
+      <c r="O3" s="3">
         <v>0.82</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="P3" s="3">
         <v>0.26</v>
       </c>
-      <c r="R3" s="4">
+      <c r="Q3" s="3">
         <v>7.4</v>
       </c>
-      <c r="S3" s="5"/>
-    </row>
-    <row r="4" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="4"/>
+    </row>
+    <row r="4" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="str">
-        <f>IF(S4=0,"H2O",IF(R4&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
+      <c r="E4" s="2">
+        <v>1100</v>
       </c>
       <c r="F4" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G4" s="2">
         <v>5309</v>
       </c>
-      <c r="H4" s="4">
+      <c r="G4" s="3">
         <v>58.41</v>
       </c>
-      <c r="I4" s="4">
+      <c r="H4" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="J4" s="4">
+      <c r="I4" s="3">
         <v>18.25</v>
       </c>
-      <c r="K4" s="4">
+      <c r="J4" s="3">
         <v>6.46</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>3.39</v>
       </c>
-      <c r="N4" s="4">
+      <c r="M4" s="3">
         <v>6.7</v>
       </c>
-      <c r="O4" s="4">
+      <c r="N4" s="3">
         <v>4.3499999999999996</v>
       </c>
-      <c r="P4" s="4">
+      <c r="O4" s="3">
         <v>0.82</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="P4" s="3">
         <v>0.26</v>
       </c>
-      <c r="R4" s="4">
+      <c r="Q4" s="3">
         <v>10.1</v>
       </c>
-      <c r="S4" s="5"/>
-    </row>
-    <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="str">
-        <f>IF(S5=0,"H2O",IF(R5&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
+      <c r="E5" s="2">
+        <v>1100</v>
       </c>
       <c r="F5" s="2">
+        <v>5309</v>
+      </c>
+      <c r="G5" s="3">
+        <v>58.41</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I5" s="3">
+        <v>18.25</v>
+      </c>
+      <c r="J5" s="3">
+        <v>6.3097000000000003</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L5" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="M5" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="N5" s="3">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.82</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>10.1</v>
+      </c>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>1100</v>
       </c>
-      <c r="G5" s="2">
-        <v>5309</v>
-      </c>
-      <c r="H5" s="4">
-        <v>58.41</v>
-      </c>
-      <c r="I5" s="4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J5" s="4">
-        <v>18.25</v>
-      </c>
-      <c r="K5" s="4">
-        <v>6.3097000000000003</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="M5" s="4">
-        <v>3.39</v>
-      </c>
-      <c r="N5" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="O5" s="4">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0.82</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0.26</v>
-      </c>
-      <c r="R5" s="4">
-        <v>10.1</v>
-      </c>
-      <c r="S5" s="5"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
+      <c r="F6">
+        <v>703</v>
+      </c>
+      <c r="G6" s="10">
+        <v>62.6</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="I6" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="J6" s="10">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="M6" s="10">
+        <v>5.64</v>
+      </c>
+      <c r="N6" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="O6" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>2.62</v>
+      </c>
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1100</v>
+      </c>
+      <c r="F7">
+        <v>703</v>
+      </c>
+      <c r="G7" s="10">
+        <v>62.6</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="I7" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="J7" s="10">
+        <v>3.8185979999999997</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="L7" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="M7" s="10">
+        <v>5.64</v>
+      </c>
+      <c r="N7" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="O7" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>2.62</v>
+      </c>
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1100</v>
+      </c>
+      <c r="F8">
+        <v>1865</v>
+      </c>
+      <c r="G8" s="10">
+        <v>62.6</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="I8" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="J8" s="10">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="M8" s="10">
+        <v>5.64</v>
+      </c>
+      <c r="N8" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="O8" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>5.03</v>
+      </c>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E9">
+        <v>1100</v>
+      </c>
+      <c r="F9">
+        <v>1865</v>
+      </c>
+      <c r="G9" s="10">
+        <v>62.6</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="I9" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="J9" s="10">
+        <v>3.8185979999999997</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="L9" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="M9" s="10">
+        <v>5.64</v>
+      </c>
+      <c r="N9" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="O9" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>5.03</v>
+      </c>
+      <c r="R9" s="11"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="10" t="str">
-        <f>IF(S6=0,"H2O",IF(R6&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F6">
-        <v>1100</v>
-      </c>
-      <c r="G6">
-        <v>703</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="E10">
+        <v>1050</v>
+      </c>
+      <c r="F10">
+        <v>2985</v>
+      </c>
+      <c r="G10" s="10">
         <v>62.6</v>
       </c>
-      <c r="I6" s="11">
+      <c r="H10" s="10">
         <v>0.63</v>
       </c>
-      <c r="J6" s="11">
+      <c r="I10" s="10">
         <v>17.3</v>
       </c>
-      <c r="K6" s="11">
+      <c r="J10" s="10">
         <v>4.0199999999999996</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11">
+      <c r="K10" s="10"/>
+      <c r="L10" s="10">
         <v>2.65</v>
       </c>
-      <c r="N6" s="11">
+      <c r="M10" s="10">
         <v>5.64</v>
       </c>
-      <c r="O6" s="11">
+      <c r="N10" s="10">
         <v>4.05</v>
       </c>
-      <c r="P6" s="11">
+      <c r="O10" s="10">
         <v>1.61</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="P10" s="10">
         <v>0.24</v>
       </c>
-      <c r="R6" s="11">
-        <v>2.62</v>
-      </c>
-      <c r="S6" s="12"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="Q10" s="10">
+        <v>6.76</v>
+      </c>
+      <c r="R10" s="11"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1050</v>
+      </c>
+      <c r="F11">
+        <v>2985</v>
+      </c>
+      <c r="G11" s="10">
+        <v>62.6</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="I11" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="J11" s="10">
+        <v>3.8185979999999997</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="L11" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="M11" s="10">
+        <v>5.64</v>
+      </c>
+      <c r="N11" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="O11" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>6.76</v>
+      </c>
+      <c r="R11" s="11"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="B12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="10" t="str">
-        <f>IF(S7=0,"H2O",IF(R7&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F7">
-        <v>1100</v>
-      </c>
-      <c r="G7">
-        <v>703</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="E12">
+        <v>1000</v>
+      </c>
+      <c r="F12">
+        <v>2830</v>
+      </c>
+      <c r="G12" s="10">
         <v>62.6</v>
       </c>
-      <c r="I7" s="11">
+      <c r="H12" s="10">
         <v>0.63</v>
       </c>
-      <c r="J7" s="11">
+      <c r="I12" s="10">
         <v>17.3</v>
       </c>
-      <c r="K7" s="11">
+      <c r="J12" s="10">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10">
+        <v>2.65</v>
+      </c>
+      <c r="M12" s="10">
+        <v>5.64</v>
+      </c>
+      <c r="N12" s="10">
+        <v>4.05</v>
+      </c>
+      <c r="O12" s="10">
+        <v>1.61</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>6.82</v>
+      </c>
+      <c r="R12" s="11"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13">
+        <v>2830</v>
+      </c>
+      <c r="G13" s="10">
+        <v>62.6</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="I13" s="10">
+        <v>17.3</v>
+      </c>
+      <c r="J13" s="10">
         <v>3.8185979999999997</v>
       </c>
-      <c r="L7" s="11">
+      <c r="K13" s="10">
         <v>0.06</v>
       </c>
-      <c r="M7" s="11">
+      <c r="L13" s="10">
         <v>2.65</v>
       </c>
-      <c r="N7" s="11">
+      <c r="M13" s="10">
         <v>5.64</v>
       </c>
-      <c r="O7" s="11">
+      <c r="N13" s="10">
         <v>4.05</v>
       </c>
-      <c r="P7" s="11">
+      <c r="O13" s="10">
         <v>1.61</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="P13" s="10">
         <v>0.24</v>
       </c>
-      <c r="R7" s="11">
-        <v>2.62</v>
-      </c>
-      <c r="S7" s="12"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="Q13" s="10">
+        <v>6.82</v>
+      </c>
+      <c r="R13" s="11"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10" t="str">
-        <f>IF(S8=0,"H2O",IF(R8&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F8">
-        <v>1100</v>
-      </c>
-      <c r="G8">
-        <v>1865</v>
-      </c>
-      <c r="H8" s="11">
-        <v>62.6</v>
-      </c>
-      <c r="I8" s="11">
-        <v>0.63</v>
-      </c>
-      <c r="J8" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="K8" s="11">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11">
-        <v>2.65</v>
-      </c>
-      <c r="N8" s="11">
-        <v>5.64</v>
-      </c>
-      <c r="O8" s="11">
-        <v>4.05</v>
-      </c>
-      <c r="P8" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="Q8" s="11">
-        <v>0.24</v>
-      </c>
-      <c r="R8" s="11">
-        <v>5.03</v>
-      </c>
-      <c r="S8" s="12"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="str">
-        <f>IF(S9=0,"H2O",IF(R9&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F9">
-        <v>1100</v>
-      </c>
-      <c r="G9">
-        <v>1865</v>
-      </c>
-      <c r="H9" s="11">
-        <v>62.6</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0.63</v>
-      </c>
-      <c r="J9" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="K9" s="11">
-        <v>3.8185979999999997</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0.06</v>
-      </c>
-      <c r="M9" s="11">
-        <v>2.65</v>
-      </c>
-      <c r="N9" s="11">
-        <v>5.64</v>
-      </c>
-      <c r="O9" s="11">
-        <v>4.05</v>
-      </c>
-      <c r="P9" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="Q9" s="11">
-        <v>0.24</v>
-      </c>
-      <c r="R9" s="11">
-        <v>5.03</v>
-      </c>
-      <c r="S9" s="12"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="str">
-        <f>IF(S10=0,"H2O",IF(R10&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F10">
+      <c r="E14">
         <v>1050</v>
       </c>
-      <c r="G10">
-        <v>2985</v>
-      </c>
-      <c r="H10" s="11">
-        <v>62.6</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0.63</v>
-      </c>
-      <c r="J10" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="K10" s="11">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11">
-        <v>2.65</v>
-      </c>
-      <c r="N10" s="11">
-        <v>5.64</v>
-      </c>
-      <c r="O10" s="11">
-        <v>4.05</v>
-      </c>
-      <c r="P10" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="Q10" s="11">
-        <v>0.24</v>
-      </c>
-      <c r="R10" s="11">
-        <v>6.76</v>
-      </c>
-      <c r="S10" s="12"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="str">
-        <f>IF(S11=0,"H2O",IF(R11&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F11">
-        <v>1050</v>
-      </c>
-      <c r="G11">
-        <v>2985</v>
-      </c>
-      <c r="H11" s="11">
-        <v>62.6</v>
-      </c>
-      <c r="I11" s="11">
-        <v>0.63</v>
-      </c>
-      <c r="J11" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="K11" s="11">
-        <v>3.8185979999999997</v>
-      </c>
-      <c r="L11" s="11">
-        <v>0.06</v>
-      </c>
-      <c r="M11" s="11">
-        <v>2.65</v>
-      </c>
-      <c r="N11" s="11">
-        <v>5.64</v>
-      </c>
-      <c r="O11" s="11">
-        <v>4.05</v>
-      </c>
-      <c r="P11" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="Q11" s="11">
-        <v>0.24</v>
-      </c>
-      <c r="R11" s="11">
-        <v>6.76</v>
-      </c>
-      <c r="S11" s="12"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="str">
-        <f>IF(S12=0,"H2O",IF(R12&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F12">
-        <v>1000</v>
-      </c>
-      <c r="G12">
-        <v>2830</v>
-      </c>
-      <c r="H12" s="11">
-        <v>62.6</v>
-      </c>
-      <c r="I12" s="11">
-        <v>0.63</v>
-      </c>
-      <c r="J12" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="K12" s="11">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11">
-        <v>2.65</v>
-      </c>
-      <c r="N12" s="11">
-        <v>5.64</v>
-      </c>
-      <c r="O12" s="11">
-        <v>4.05</v>
-      </c>
-      <c r="P12" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="Q12" s="11">
-        <v>0.24</v>
-      </c>
-      <c r="R12" s="11">
-        <v>6.82</v>
-      </c>
-      <c r="S12" s="12"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10" t="str">
-        <f>IF(S13=0,"H2O",IF(R13&lt;0.4,"CO2","none"))</f>
-        <v>H2O</v>
-      </c>
-      <c r="F13">
-        <v>1000</v>
-      </c>
-      <c r="G13">
-        <v>2830</v>
-      </c>
-      <c r="H13" s="11">
-        <v>62.6</v>
-      </c>
-      <c r="I13" s="11">
-        <v>0.63</v>
-      </c>
-      <c r="J13" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="K13" s="11">
-        <v>3.8185979999999997</v>
-      </c>
-      <c r="L13" s="11">
-        <v>0.06</v>
-      </c>
-      <c r="M13" s="11">
-        <v>2.65</v>
-      </c>
-      <c r="N13" s="11">
-        <v>5.64</v>
-      </c>
-      <c r="O13" s="11">
-        <v>4.05</v>
-      </c>
-      <c r="P13" s="11">
-        <v>1.61</v>
-      </c>
-      <c r="Q13" s="11">
-        <v>0.24</v>
-      </c>
-      <c r="R13" s="11">
-        <v>6.82</v>
-      </c>
-      <c r="S13" s="12"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
+      <c r="F14" s="12">
+        <v>5000</v>
+      </c>
+      <c r="G14">
+        <v>58.82</v>
+      </c>
+      <c r="H14">
+        <v>0.51</v>
+      </c>
+      <c r="I14">
+        <v>20.91</v>
+      </c>
+      <c r="J14">
+        <v>3.36</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0.16</v>
+      </c>
+      <c r="M14">
+        <v>6.73</v>
+      </c>
+      <c r="N14">
+        <v>4.3</v>
+      </c>
+      <c r="O14">
+        <v>3.92</v>
+      </c>
+      <c r="P14">
+        <v>1.28</v>
+      </c>
+      <c r="Q14">
+        <v>7.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
